--- a/docs/08_haip-requirements-catalog.xlsx
+++ b/docs/08_haip-requirements-catalog.xlsx
@@ -12,8 +12,8 @@
     <sheet name="2_OID4VCI_Metadataパラメータ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_HAIP要件カタログ'!$A$4:$F$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_OID4VCI_Metadataパラメータ'!$A$4:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1_HAIP要件カタログ'!$A$4:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2_OID4VCI_Metadataパラメータ'!$A$4:$F$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,10 +69,19 @@
       <sz val="9"/>
     </font>
     <font>
+      <name val="Consolas"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <color rgb="00555555"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001155CC"/>
+      <sz val="9"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -102,7 +111,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +136,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -186,18 +200,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,23 +242,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,10 +278,13 @@
     <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -629,16 +652,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>OID4VC / HAIP 要件カタログ(全レベル)</t>
+          <t>OID4VC / HAIP 要件カタログ(全レベル・サンプル・参照リンク付き)</t>
         </is>
       </c>
     </row>
@@ -655,14 +678,14 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VC 発行・VP 検証の「フローそのもの」だけでなく、エコシステム要件・Issuer Metadata・暗号/ハッシュ・</t>
+          <t>発行・検証フローだけでなく、エコシステム要件・Issuer Metadata・暗号/ハッシュ・Attestation も含めた HAIP 要件を、</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Attestation など、HAIP が定める要件を MUST だけでなく SHOULD / MAY / MUST NOT まで含めて一覧化しています。</t>
+          <t>MUST/SHOULD/MAY/MUST NOT の全レベルで一覧化。各項目にサンプルデータと、仕様書の該当箇所への参照リンクを付与しています。</t>
         </is>
       </c>
     </row>
@@ -679,21 +702,21 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>・シート「1_HAIP要件カタログ」: HAIP が上乗せ・必須化する要件を 7 カテゴリ(A〜G)で整理。レベル列で MUST/SHOULD 等を色分け。</t>
+          <t>・「1_HAIP要件カタログ」: HAIP が上乗せ・必須化する要件を 7 カテゴリ(A〜G)で整理。レベル/サンプル/参照リンク列付き。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>・シート「2_OID4VCI_Metadataパラメータ」: 素の OID4VCI が定義するメタデータ/Offer/Request・Response の全パラメータと REQUIRED/OPTIONAL。</t>
+          <t>・「2_OID4VCI_Metadataパラメータ」: 素の OID4VCI のメタデータ/Offer/Request・Response 全パラメータ。サンプル値/参照リンク列付き。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>・別ファイル docs/07_haip-diff-matrix.xlsx: HAIP と素の OID4VCI/OID4VP の MUST・任意「差分」比較(発行・検証・フォーマット)。</t>
+          <t>・別ファイル docs/07_haip-diff-matrix.xlsx: HAIP と素の OID4VCI/OID4VP の MUST・任意「差分」比較。</t>
         </is>
       </c>
     </row>
@@ -717,7 +740,7 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>推奨=SHOULD/RECOMMENDED   非推奨=SHOULD NOT/NOT RECOMMENDED   任意=MAY/OPTIONAL</t>
+          <t>推奨=SHOULD/RECOMMENDED   非推奨=NOT RECOMMENDED   任意=MAY/OPTIONAL</t>
         </is>
       </c>
     </row>
@@ -727,42 +750,69 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ 出典と注意</t>
+          <t>■ サンプル列について</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>・HAIP: GitHub openid/OpenID4VC-HAIP の draft-06(2025-11-20、Final 直前版)を直接確認。</t>
+          <t>仕様の記法に沿った代表的な値の例です。値(コード・トークン・ハッシュ等)はダミーで、長い文字列は「…」で省略しています。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>・OID4VCI: 1.0-final(2025-09-16)/ OID4VP: 1.0-final(2025-07-10)を直接確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>・openid.net への直接アクセスは環境制約で不可のため、同一内容を管理する OpenID Foundation の GitHub ソースを参照。</t>
+      <c r="A18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 参照リンクについて</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>・draft-06 → HAIP 1.0 Final(2025-12)間の差分は未検証。実装確定時は各仕様の Final 本文を一次情報として必ず確認してください。</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>リンクは openid.net の各 Final 仕様ページを指します。# 以降のアンカーは xml2rfc 標準命名(#name-&lt;セクション名&gt;)に基づく best-effort です。</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>・要件レベルは原文の助動詞(MUST/SHOULD/MAY 等)に基づき分類。条件付き項目は「補足」列に条件を明記。</t>
+          <t>万一アンカーがずれてもページ先頭に着地するだけなので、併記の「§セクション名」をページ内検索(Ctrl+F)すれば該当箇所を特定できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>■ 出典と注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>・HAIP: GitHub openid/OpenID4VC-HAIP の draft-06(2025-11-20、Final直前版)を直接確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>・OID4VCI: 1.0-final(2025-09-16)/ OID4VP: 1.0-final(2025-07-10)を直接確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>・draft-06 → HAIP 1.0 Final(2025-12)間の差分は未検証。実装確定時は各仕様の Final 本文を一次情報として必ず確認してください。</t>
         </is>
       </c>
     </row>
@@ -777,35 +827,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>HAIP 要件カタログ — エコシステム / Issuerメタデータ / 暗号 / Attestation 等を含む全要件(MUST/SHOULD/MAY レベル別)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>HAIP 要件カタログ — 全レベル(MUST/SHOULD/MAY/MUST NOT)+ サンプル + 参照リンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>出典: HAIP draft-06(2025-11-20、Final直前版)。原文の MUST/MUST NOT/SHOULD/RECOMMENDED/MAY を日本語レベルに対応。draft-06→Final(2025-12)差分は未検証。実装確定は Final 本文を要確認。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
+          <t>出典: HAIP draft-06(2025-11-20)。参照リンクは openid.net の HAIP/OID4VCI/OID4VP Final ページ。アンカーは xml2rfc標準命名(#name-…)に基づく best-effort。リンクがずれた場合も併記のセクション名で検索可能。draft-06→Final差分は未検証。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>凡例:  必須=MUST/REQUIRED   禁止=MUST NOT   条件付き必須=条件によりMUST   推奨=SHOULD/RECOMMENDED   非推奨=SHOULD NOT/NOT RECOMMENDED   任意=MAY/OPTIONAL</t>
+          <t>凡例:  必須=MUST/REQUIRED   禁止=MUST NOT   条件付き必須=条件によりMUST   推奨=SHOULD/RECOMMENDED   非推奨=NOT RECOMMENDED   任意=MAY/OPTIONAL</t>
         </is>
       </c>
     </row>
@@ -832,12 +883,17 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>補足 / 必須(推奨)である理由</t>
+          <t>サンプル / 例</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>原文の語 / 該当箇所</t>
+          <t>補足・理由(＋原文の語)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>参照(仕様・セクション)</t>
         </is>
       </c>
     </row>
@@ -852,8 +908,9 @@
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="10" t="n"/>
       <c r="F5" s="10" t="n"/>
-    </row>
-    <row r="6" ht="57" customHeight="1">
+      <c r="G5" s="10" t="n"/>
+    </row>
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
           <t>対応フォーマットの明示(SD-JWT VC / mdoc / 両方)</t>
@@ -871,24 +928,29 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>どのクレデンシャルフォーマットのサポートを必須とするかを、エコシステムが明確に示すべき。</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>ウォレット・発行者・検証者が同じフォーマットを実装するよう揃えるため。</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>Ecosystems SHOULD clearly indicate which formats...are required</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>発行の起点(Issuer-initiated / Wallet-initiated)の明示</t>
+          <t>どのフォーマットのサポートを必須とするかをエコシステムが明示すべき。</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>(方針例)「本エコシステムでは dc+sd-jwt を必須、mso_mdoc は任意」等をポリシー文書で規定</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>実装フォーマットを揃え相互接続を保証するため。原文: Ecosystems SHOULD clearly indicate which formats...</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="87" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>発行の起点(Issuer-/Wallet-initiated)の明示</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
@@ -896,34 +958,39 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>発行者起点・ウォレット起点のどちら(または両方)をサポートすべきかを示す。</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>実装範囲を揃え、相互接続の前提を明確化するため。</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>Ecosystems SHOULD clearly indicate whether...Issuer-initiated, Wallet-initiated...or both</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="57" customHeight="1">
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>発行者起点・ウォレット起点のどちら(両方)を必須とするか示す。</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>(方針例)「Issuer-initiated と Wallet-initiated の両方をサポート必須」</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>実装範囲を揃えるため。原文: Ecosystems SHOULD clearly indicate whether...Issuer-initiated, Wallet-initiated...or both</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Issuer-initiated 時の Credential Offer 利用</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -935,22 +1002,27 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>発行者起点フローをサポートする場合は Credential Offer を用いる。</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>起点フローの手順を統一するため。</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>If Issuer-initiated flows are supported, they MUST use the Credential Offer</t>
+          <t>発行者起点をサポートするなら Credential Offer を用いる。</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>openid-credential-offer://?credential_offer_uri=https%3A%2F%2Fissuer.example.com%2Foffers%2F123</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>起点フローの手順統一。原文: If Issuer-initiated flows are supported, they MUST use the Credential Offer</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Credential Offer</t>
         </is>
       </c>
     </row>
     <row r="9" ht="57" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Wallet Attestation フォーマット(Appendix E)の要求</t>
         </is>
@@ -960,24 +1032,29 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>ウォレット⇔発行者の相互運用を求めるなら、Appendix E の Wallet Attestation 形式を要求すべき。</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>相互運用が目的の場合の推奨。代替形式に依存することも MAY で許容。</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>Ecosystems...SHOULD require...Appendix E / MAY choose other formats</t>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>相互運用を求めるなら Appendix E の Wallet Attestation 形式を要求すべき(代替は任意)。</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>(方針例)「Wallet Attestation は HAIP Appendix E 形式を必須」</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>相互運用が目的の場合の推奨。原文: SHOULD require...Appendix E / MAY choose other formats</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
         </is>
       </c>
     </row>
@@ -999,49 +1076,59 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>鍵証明レベルの相互運用を求めるなら、Appendix D の Key Attestation 形式を要求すべき。</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>相互運用が目的の場合の推奨。代替形式に依存することも MAY。</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>Ecosystems...SHOULD require...Appendix D / MAY choose other formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+          <t>鍵証明の相互運用を求めるなら Appendix D 形式を要求すべき(代替は任意)。</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>(方針例)「Key Attestation は HAIP Appendix D 形式を必須」</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>相互運用が目的の場合の推奨。原文: SHOULD require...Appendix D / MAY choose other formats</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Key Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>追加ハッシュアルゴリズムの mandate</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>エコシステム</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>エコシステム固有プロファイルで、SHA-256 以外のハッシュを追加で必須化してもよい。</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>地域・業界固有の要件に対応するための拡張余地。</t>
-        </is>
-      </c>
-      <c r="F11" s="19" t="inlineStr">
-        <is>
-          <t>Ecosystem-specific profiles...MAY mandate additional hashing algorithms</t>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>エコシステム固有プロファイルで SHA-256 以外を追加必須化してもよい。</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>(方針例)「SHA-384 を追加で必須化」</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>地域・業界固有要件への拡張余地。原文: Ecosystem-specific profiles...MAY mandate additional hashing algorithms</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Hash Algorithms</t>
         </is>
       </c>
     </row>
@@ -1056,14 +1143,15 @@
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
       <c r="F12" s="10" t="n"/>
-    </row>
-    <row r="13" ht="57" customHeight="1">
+      <c r="G12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
           <t>署名付き Credential Issuer Metadata の対応</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -1075,49 +1163,59 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>TLS だけでは足りない発行者認証が必要な場合、署名付きメタデータ(OID4VCI 11.2.3)に対応する。</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>高い保証レベルで発行者の真正性を担保するため。x5c で鍵解決、自己署名不可・トラストアンカー非内包。</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>signed Credential Issuer Metadata...MUST be supported (条件付き)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+          <t>TLS 超の発行者認証が必要な場合、署名付きメタデータに対応する。</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>"signed_metadata": "eyJhbGciOiJFUzI1NiIsIng1YyI6WyJNSUlD..."</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>高保証で発行者の真正性を担保するため。原文: signed Credential Issuer Metadata...MUST be supported(条件付き)</t>
+        </is>
+      </c>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="87" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>全 Credential Configuration への scope 付与</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>サポートする各 Credential Configuration にメタデータ上 scope を含める。</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>認可コードフローで scope によりクレデンシャル種別を識別するため。</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>metadata MUST include a scope for every Credential Configuration</t>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>各 Credential Configuration にメタデータ上 scope を含める。</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>"credential_configurations_supported": { "EmployeeCredential": { "scope": "employee_credential", ... } }</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>認可コードフローで scope により種別識別するため。原文: metadata MUST include a scope for every Credential Configuration</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Issuer Metadata</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1225,7 @@
           <t>nonce_endpoint の提示(key binding 対応時)</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -1139,59 +1237,69 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>cryptographic_binding_methods_supported を示す構成があれば nonce_endpoint を必須で公開。</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>proof に c_nonce を入れリプレイを防ぐため。</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>the nonce_endpoint MUST be present (条件付き)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="57" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+          <t>cryptographic_binding_methods_supported があれば nonce_endpoint を公開。</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>"nonce_endpoint": "https://issuer.example.com/nonce"</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>proof に c_nonce を入れリプレイ防止。原文: the nonce_endpoint MUST be present(条件付き)</t>
+        </is>
+      </c>
+      <c r="G15" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Nonce Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>メタデータ画像の SVG/PNG 両対応(Wallet)</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>メタデータ内の画像をレンダリングするウォレットは SVG と PNG の両形式に対応する。</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>発行者が用意した表示画像を確実に描画できるようにするため。</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>Such wallets MUST support both the SVG and PNG formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>メタデータ画像をレンダリングするウォレットは SVG・PNG 両対応。</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>"logo": { "uri": "https://issuer.example.com/logo.svg", "alt_text": "Example Bank" }</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>発行者提供の表示画像を確実に描画するため。原文: MUST support both the SVG and PNG formats</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="57" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
           <t>画像の data URI / HTTPS URL 両対応(Wallet)</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1203,49 +1311,59 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>画像を data URI 経由でも HTTPS URL 経由でも取得・表示できる。</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>画像配信方式の差異による表示崩れを防ぐため。</t>
-        </is>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>MUST support images...both data URIs and HTTPS URLs</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="72" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+          <t>画像を data URI・HTTPS URL のどちらでも取得表示できる。</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>"uri": "data:image/png;base64,iVBORw0KGgoAAAANS..."</t>
+        </is>
+      </c>
+      <c r="F17" s="16" t="inlineStr">
+        <is>
+          <t>配信方式差による表示崩れ防止。原文: MUST support images...both data URIs and HTTPS URLs</t>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="87" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>batch 発行可否の明示(batch_credential_issuance)</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>batch_credential_issuance メタデータの有無で、バッチ発行対応を明示する。</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>ウォレットが 1 回で複数取得できるかを判断できるようにするため。</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Issuer MUST indicate whether batch issuance is supported...by including or omitting</t>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>batch_credential_issuance の有無でバッチ発行対応を明示。</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>"batch_credential_issuance": { "batch_size": 10 }</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>1回で複数取得可否をウォレットが判断するため。原文: Issuer MUST indicate whether batch issuance is supported...by including or omitting</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
@@ -1260,14 +1378,15 @@
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
       <c r="F19" s="10" t="n"/>
-    </row>
-    <row r="20" ht="57" customHeight="1">
+      <c r="G19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>ES256(ECDSA P-256 + SHA-256)の最低サポート</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+          <t>ES256(ECDSA P-256 + SHA-256)最低サポート</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1279,22 +1398,27 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>全エンティティが署名操作で最低限 ES256(COSE では -7/-9)をサポートする。</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>共通の署名アルゴリズムを保証し、署名検証の不一致による接続断を防ぐため。</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>MUST, at a minimum, support ECDSA with P-256 and SHA-256 (ES256)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="57" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+          <t>全エンティティが署名操作で最低限 ES256(COSE -7/-9)をサポート。</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>{ "alg": "ES256" }   /   COSE: -7</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>共通署名アルゴリズムを保証し検証不一致を防ぐ。原文: MUST, at a minimum, support ECDSA with P-256 and SHA-256 (ES256)</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Crypto Suites</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="72" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>併用アルゴリズムの metadata 明示</t>
         </is>
@@ -1304,34 +1428,39 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>各エンティティ</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>他の暗号スイートを併用する場合、対応アルゴリズム・鍵種別を metadata で明示すべき。</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>相手方がネゴシエーションで適切なアルゴリズムを選べるようにするため。</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>each entity SHOULD make it explicit in its metadata which other algorithms...</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="57" customHeight="1">
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>他の暗号スイート併用時、対応アルゴリズム・鍵種別を metadata で明示すべき。</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>"credential_signing_alg_values_supported": ["ES256","ES384"]</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>ネゴシエーションのため。原文: each entity SHOULD make it explicit in its metadata which other algorithms...</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Crypto Suites</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
         <is>
           <t>SHA-256 のサポート</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1346,19 +1475,24 @@
           <t>SD-JWT VC・mdoc のダイジェスト生成/検証に SHA-256 を用いる。</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>選択的開示のハッシュ照合を全実装で成立させるため。</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>The hash algorithm SHA-256 MUST be supported by all the entities</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="57" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>"_sd_alg": "sha-256"</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>選択的開示のハッシュ照合を全実装で成立させるため。原文: The hash algorithm SHA-256 MUST be supported by all the entities</t>
+        </is>
+      </c>
+      <c r="G22" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Hash Algorithms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="72" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>併用ハッシュの metadata 明示</t>
         </is>
@@ -1368,24 +1502,29 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>各エンティティ</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>他のハッシュを併用する場合、対応ハッシュを metadata で明示すべき。</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>ハッシュ方式のネゴシエーションのため。</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>each entity SHOULD make it explicit in its metadata which other algorithms</t>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>他ハッシュ併用時、対応ハッシュを metadata で明示すべき。</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>(metadata で対応ハッシュを列挙)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>ハッシュ方式のネゴシエーション。原文: each entity SHOULD make it explicit in its metadata which other algorithms</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Hash Algorithms</t>
         </is>
       </c>
     </row>
@@ -1400,14 +1539,15 @@
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
       <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="57" customHeight="1">
+      <c r="G24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Wallet Attestation によるクライアント認証</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1422,56 +1562,66 @@
           <t>OAuth2 エンドポイントで Wallet Attestation を用いたクライアント認証を行う。</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
-        <is>
-          <t>正規ウォレットのみに発行を限定し、なりすましを排除するため。</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Wallets MUST perform client authentication with the Wallet Attestation</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="57" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>OAuth-Client-Attestation: eyJhbGciOiJFUzI1NiIsInR5cCI6Im9hdXRoLWNsaWVudC1hdHRlc3RhdGlvbitqd3Qi...</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>正規ウォレットのみに発行を限定するため。原文: Wallets MUST perform client authentication with the Wallet Attestation</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Wallet Attestation の x5c に公開鍵証明書</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>検証鍵(と信頼チェーン)を x5c JOSE ヘッダに含める。</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>発行者が JWKS 参照なしに検証できるようにするため。</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>the public key certificate...MUST be included in the x5c JOSE header</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="57" customHeight="1">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>{ "typ": "oauth-client-attestation+jwt", "alg": "ES256", "x5c": ["MIIC..."] }</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>JWKS 参照なしで検証するため。原文: the public key certificate...MUST be included in the x5c JOSE header</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Wallet Attestation の Issuer 間再利用の禁止</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
@@ -1483,59 +1633,69 @@
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>同一の Wallet Attestation を異なる発行者にまたいで使い回してはならない。</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>発行者をまたいだ名寄せ(トラッキング)を防ぐため。</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
-        <is>
-          <t>Wallet Attestations MUST NOT be reused across different Issuers</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="72" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+          <t>同一 Attestation を異なる発行者にまたいで使い回してはならない。</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>(発行者ごとに別個の Attestation を取得。使い回し不可)</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>発行者をまたいだ名寄せ防止。原文: Wallet Attestations MUST NOT be reused across different Issuers</t>
+        </is>
+      </c>
+      <c r="G27" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="87" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>インスタンス固有識別子の混入禁止</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>個々のウォレットインスタンスを一意に識別する値を含めてはならない。sub は全インスタンス共通値。</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>個体識別による追跡を防ぐため(unlinkability)。</t>
-        </is>
-      </c>
-      <c r="F28" s="19" t="inlineStr">
-        <is>
-          <t>MUST NOT introduce a unique identifier...sub...MUST be shared by all instances</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="42" customHeight="1">
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>個々のインスタンスを一意識別する値を含めない。sub は全インスタンス共通値。</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>"sub": "https://wallet.example.com/product/MyWalletApp"  (全端末で同一)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>個体追跡防止(unlinkability)。原文: MUST NOT introduce a unique identifier...sub...MUST be shared by all instances</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Wallet Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="72" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Key Attestation のサポート</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1547,53 +1707,63 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>proof の鍵がセキュアな環境で保持されることを示す Key Attestation に対応する。</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>鍵の保管品質(WSCD等)を発行者が確認できるようにするため。</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>Wallets MUST support key attestations</t>
+          <t>proof の鍵がセキュアな環境で保持されることを示す Key Attestation に対応。</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>{ "typ": "key-attestation+jwt", "attested_keys": [ { "kty":"EC","crv":"P-256","x":"...","y":"..." } ] }</t>
+        </is>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>鍵保管品質(WSCD等)を発行者が確認するため。原文: Wallets MUST support key attestations</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Key Attestation</t>
         </is>
       </c>
     </row>
     <row r="30" ht="72" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Key Attestation(Appendix D)の x5c 要件</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="D30" s="18" t="inlineStr">
-        <is>
-          <t>Appendix D 形式使用時、検証鍵を x5c に含める。トラストアンカー非内包・自己署名不可。</t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>署名検証と信頼判定を X.509 で一貫させるため。</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>MUST be included in the x5c / MUST NOT be self-signed / trust anchor MUST NOT be included</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="57" customHeight="1">
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Appendix D 形式使用時、検証鍵を x5c に含める。自己署名不可・アンカー非内包。</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>{ "typ": "key-attestation+jwt", "alg": "ES256", "x5c": ["MIIC..."] }</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>署名検証と信頼判定を X.509 で一貫。原文: MUST be included in the x5c / MUST NOT be self-signed</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Key Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>バッチ時の単一 attestation への集約</t>
@@ -1614,53 +1784,63 @@
           <t>バッチ発行で複数鍵を使う場合、全鍵を単一の Key Attestation で証明すべき。</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>検証負荷とラウンドトリップを抑えるため。</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>all public keys...SHOULD be attested within a single key attestation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="57" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>"attested_keys": [ {key1}, {key2}, {key3} ]  (1つの attestation に集約)</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>検証負荷とラウンドトリップ削減。原文: all public keys...SHOULD be attested within a single key attestation</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Key Attestation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Wallet Attestation バックエンドのプライバシー設計</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Wallet Provider</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>Attestation を発行するバックエンドは利用者のプライバシーを考慮して設計する。</t>
-        </is>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>バックエンドが利用状況を収集・追跡しない設計にするため。</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>Such a backend service MUST be designed considering the privacy of its users</t>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>Attestation を発行するバックエンドは利用者プライバシーを考慮して設計する。</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>(バックエンドが利用状況を収集・追跡しない設計)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>バックエンドによる追跡防止。原文: Such a backend service MUST be designed considering the privacy of its users</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Privacy Considerations</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>E. 発行フロー(SHOULD/RECOMMENDED を含む補足)</t>
+          <t>E. 発行フロー(SHOULD/RECOMMENDED 補足)</t>
         </is>
       </c>
       <c r="B33" s="10" t="n"/>
@@ -1668,8 +1848,9 @@
       <c r="D33" s="10" t="n"/>
       <c r="E33" s="10" t="n"/>
       <c r="F33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
+      <c r="G33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="57" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Refresh Token の対応</t>
@@ -1687,53 +1868,63 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>クレデンシャル更新のため Refresh Token をサポートすることが推奨される。</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>有効期限切れ前の再発行をスムーズにするため。</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Refresh tokens are RECOMMENDED to be supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="57" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+          <t>クレデンシャル更新のため Refresh Token をサポートすることが推奨。</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>"refresh_token": "8xLOxBtZp8...", "expires_in": 86400</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>有効期限切れ前の再発行を円滑化。原文: Refresh tokens are RECOMMENDED to be supported</t>
+        </is>
+      </c>
+      <c r="G34" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Token Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="72" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>長期経過後の Refresh Token 利用</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>非推奨</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>発行から長期間(例: 1年超)経過後の refresh token 利用は推奨されない。</t>
-        </is>
-      </c>
-      <c r="E35" s="18" t="inlineStr">
-        <is>
-          <t>古い本人確認状態のまま更新し続けることを避けるため。</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>usage of the refresh tokens is NOT RECOMMENDED (after e.g. a year)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="57" customHeight="1">
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>発行から長期間(例:1年超)経過後の refresh token 利用は推奨されない。</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>(発行から一定期間で refresh を打ち切り、再発行フローへ誘導)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>古い本人確認状態での更新継続を避ける。原文: usage of the refresh tokens is NOT RECOMMENDED(after e.g. a year)</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §Token Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="72" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>バッチ発行の利用(対応時)</t>
@@ -1751,22 +1942,27 @@
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>バッチ発行が使えるなら、連続リクエストではなくバッチを使うべき。</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>効率化とサーバ負荷軽減のため。</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>the Wallet SHOULD use it rather than making consecutive requests</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+          <t>バッチ発行が使えるなら連続リクエストよりバッチを使うべき。</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>"proofs": { "jwt": ["eyJ...proof1","eyJ...proof2","eyJ...proof3"] }</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>効率化とサーバ負荷軽減。原文: the Wallet SHOULD use it rather than making consecutive requests</t>
+        </is>
+      </c>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Credential Endpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="57" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>SD-JWT VC 有効期間の制限</t>
         </is>
@@ -1776,34 +1972,39 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>SD-JWT VC 発行時は有効期間を制限することが推奨される。</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>漏えい時の影響範囲を時間的に限定するため。</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>RECOMMENDED that Issuers limit the validity period</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="57" customHeight="1">
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>SD-JWT VC 発行時は有効期間を制限することが推奨。</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>"iat": 1767225600, "exp": 1769817600  (約30日)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>漏えい時の影響を時間的に限定。原文: RECOMMENDED that Issuers limit the validity period</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="72" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
           <t>有効期間表現(exp / status / 両方)</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1815,56 +2016,66 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>有効期間を設ける場合、exp クレーム・status クレーム・その両方のいずれかを用いる。</t>
-        </is>
-      </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>有効性・失効を機械的に判定可能にするため。</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>the Issuer MUST use an exp claim, a status claim, or both</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="57" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+          <t>有効期間を設ける場合、exp・status・両方のいずれかを用いる。</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>"exp": 1769817600   または   "status": { "status_list": { "idx": 412, "uri": "..." } }</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>有効性・失効を機械判定可能に。原文: the Issuer MUST use an exp claim, a status claim, or both</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="72" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>一意・予測不能な status list index</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Issuer</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
-        <is>
-          <t>各クレデレンシャルに固有で予測不能な status list インデックスを割り当てる。</t>
-        </is>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>インデックスから他クレデンシャルを推測されないようにするため(privacy)。</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>Each Credential MUST have its own unique, unpredictable status list index</t>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>各クレデンシャルに固有で予測不能な status list インデックスを割り当てる。</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>"status": { "status_list": { "idx": 293857, "uri": "https://issuer.example.com/statuslists/1" } }</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>インデックスから他クレデンシャル推測を防ぐ。原文: Each Credential MUST have its own unique, unpredictable status list index</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §IETF SD-JWT VC</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>F. 提示・検証フロー(SHOULD/MUST の補足)</t>
+          <t>F. 提示・検証フロー(SHOULD/MUST 補足)</t>
         </is>
       </c>
       <c r="B40" s="10" t="n"/>
@@ -1872,14 +2083,15 @@
       <c r="D40" s="10" t="n"/>
       <c r="E40" s="10" t="n"/>
       <c r="F40" s="10" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1">
+      <c r="G40" s="10" t="n"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>same-device フローの対応</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1894,21 +2106,26 @@
           <t>同一端末内でのリダイレクト提示フローに両者が対応する。</t>
         </is>
       </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>最も安全性の高い提示経路を共通の基盤として保証するため。</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>MUST support the 'same-device' flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>same-device フローのみ利用</t>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>openid4vp://?client_id=x509_hash%3A...&amp;request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd</t>
+        </is>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>最も安全な提示経路を共通基盤化。原文: MUST support the 'same-device' flow</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="57" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>same-device のみ利用</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -1916,34 +2133,39 @@
           <t>推奨</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Verifier</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
-        <is>
-          <t>検証者は原則 same-device フローのみを使うことが推奨される。</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>cross-device 特有のセキュリティリスクを避けるため。</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>RECOMMENDED to use only the 'same-device' flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="57" customHeight="1">
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>検証者は原則 same-device フローのみを使うことが推奨。</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>(cross-device が必要な特定要件がない限り same-device のみ提供)</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>cross-device 特有リスク回避。原文: RECOMMENDED to use only the 'same-device' flow</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="72" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
           <t>redirect_uri の応答内包と追従</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -1955,59 +2177,69 @@
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>検証者は応答に redirect_uri を含め、ウォレットはそれに追従。戻らなければ提示を拒否。</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>セッションの完了確認とセッション固定攻撃対策のため。</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="inlineStr">
-        <is>
-          <t>MUST include redirect_uri / MUST follow / MUST reject if not followed</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="72" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+          <t>検証者は応答に redirect_uri を含め、ウォレットは追従。戻らなければ提示を拒否。</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>{ "redirect_uri": "https://verifier.example.com/cb?response_code=091535f699ea575c7937fa5f0f454aee" }</t>
+        </is>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>セッション完了確認とセッション固定攻撃対策。原文: MUST include redirect_uri / MUST follow / MUST reject if not followed</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="87" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>レスポンス暗号 enc の対応(A128GCM/A256GCM)</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>検証者は A128GCM と A256GCM の両方を、ウォレットは少なくとも一方を対応。両対応時は A256GCM を使用(SHOULD)。</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>レスポンス暗号化の相互運用を担保しつつ、より強い暗号を優先するため。</t>
-        </is>
-      </c>
-      <c r="F44" s="19" t="inlineStr">
-        <is>
-          <t>Verifiers...both MUST be supported / Wallets...MUST support one or both / SHOULD use A256GCM</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="72" customHeight="1">
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>検証者は両方、ウォレットは少なくとも一方。両対応時は A256GCM 使用(SHOULD)。</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>{ "alg": "ECDH-ES", "enc": "A256GCM", "epk": { "kty":"EC","crv":"P-256","x":"...","y":"..." } }</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>暗号化の相互運用を担保しつつ強い暗号を優先。原文: both MUST be supported / Wallets MUST support one or both / SHOULD use A256GCM</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="inlineStr">
+        <is>
+          <t>OID4VP §Response Encryption</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="87" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
           <t>認可リクエストごとのエフェメラル暗号鍵</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2022,14 +2254,19 @@
           <t>レスポンス暗号化の公開鍵をリクエストごとに使い捨てにする。</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>鍵の使い回しによるレスポンス相関(追跡)を防ぐため。</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr">
-        <is>
-          <t>Verifiers MUST supply ephemeral encryption public keys specific to each request</t>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>"client_metadata": { "jwks": { "keys": [ { "kty":"EC","use":"enc","crv":"P-256","x":"...","y":"..." } ] } }</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>鍵使い回しによるレスポンス相関(追跡)防止。原文: Verifiers MUST supply ephemeral encryption public keys specific to each request</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations</t>
         </is>
       </c>
     </row>
@@ -2044,14 +2281,15 @@
       <c r="D46" s="10" t="n"/>
       <c r="E46" s="10" t="n"/>
       <c r="F46" s="10" t="n"/>
-    </row>
-    <row r="47" ht="42" customHeight="1">
+      <c r="G46" s="10" t="n"/>
+    </row>
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
           <t>haip-vci://(発行の呼び出し)</t>
         </is>
       </c>
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2066,63 +2304,112 @@
           <t>発行時にウォレットを起動するカスタム URL スキームとして使用してもよい。</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>DC API 等が使えない環境での起動手段。エコシステムが別方式を定めても可。</t>
-        </is>
-      </c>
-      <c r="F47" s="15" t="inlineStr">
-        <is>
-          <t>the custom URL scheme haip-vci:// MAY be supported</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="42" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>haip-vci://?credential_offer_uri=https%3A%2F%2Fissuer.example.com%2Foffers%2F123</t>
+        </is>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>DC API 不可環境での起動手段。原文: the custom URL scheme haip-vci:// MAY be supported</t>
+        </is>
+      </c>
+      <c r="G47" s="17" t="inlineStr">
+        <is>
+          <t>HAIP §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>haip-vp://(提示の呼び出し)</t>
         </is>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Verifier/Wallet</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>提示時にウォレットを起動するカスタム URL スキームとして使用してもよい。</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>同上(提示側)。</t>
-        </is>
-      </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>the custom URL scheme haip-vp:// MAY be supported</t>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>haip-vp://?client_id=x509_hash%3A...&amp;request_uri=https%3A%2F%2Fverifier.example.com%2Freq%2F5Fd</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>同上(提示側)。原文: the custom URL scheme haip-vp:// MAY be supported</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>HAIP §OpenID for Verifiable Presentations via Redirects</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F48"/>
+  <autoFilter ref="A4:G48"/>
   <mergeCells count="10">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2133,26 +2420,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>OID4VCI 1.0 素の仕様 — Credential Issuer Metadata / Offer / Request・Response の全パラメータと要件レベル</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>OID4VCI 1.0 素の仕様 — メタデータ/Offer/Request・Response の全パラメータ + サンプル値 + 参照リンク</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>出典: OpenID4VCI 1.0-final(2025-09-16)。.well-known/openid-credential-issuer 等で流通するパラメータ。REQUIRED/OPTIONAL/CONDITIONAL は原文表記に対応(REQUIRED=必須, OPTIONAL=任意, CONDITIONAL=条件付き必須)。</t>
+          <t>出典: OpenID4VCI 1.0-final(2025-09-16)。REQUIRED=必須, OPTIONAL=任意, CONDITIONAL=条件付き必須。参照リンクは openid.net Final ページ(#name-… は best-effort、併記セクション名で検索可)。</t>
         </is>
       </c>
     </row>
@@ -2182,6 +2471,16 @@
       <c r="D4" s="8" t="inlineStr">
         <is>
           <t>概要 / 条件</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>サンプル値(例)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>参照(仕様・セクション)</t>
         </is>
       </c>
     </row>
@@ -2194,14 +2493,16 @@
       <c r="B5" s="10" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>credential_issuer</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2216,36 +2517,56 @@
           <t>Credential Issuer の識別子(URL)。</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com"</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>credential_configurations_supported</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Issuer Metadata</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>発行可能なクレデンシャル構成のカタログ。1 件以上。</t>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>発行可能なクレデンシャル構成のカタログ。1件以上。</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>{ "EmployeeCredential": { "format": "dc+sd-jwt", "scope": "employee_credential", ... } }</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>credential_endpoint</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2260,36 +2581,56 @@
           <t>VC を発行する Credential Endpoint の URL。</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com/credential"</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>authorization_servers</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Issuer Metadata</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>利用する認可サーバー。複数 AS 構成時に指定。</t>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>利用する認可サーバー。複数AS構成時に指定。</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>["https://as.example.com"]</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="10" ht="57" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>nonce_endpoint</t>
         </is>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2301,39 +2642,59 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>c_nonce を払い出す Nonce Endpoint(HAIP では key binding 時に実質必須)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+          <t>c_nonce を払い出す Nonce Endpoint(HAIPでは key binding 時に実質必須)。</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com/nonce"</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>deferred_credential_endpoint</t>
         </is>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Issuer Metadata</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>遅延発行に対応する場合の取得エンドポイント。</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com/deferred"</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>notification_endpoint</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2348,36 +2709,56 @@
           <t>発行結果通知を受ける場合のエンドポイント。</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com/notification"</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="87" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>credential_response_encryption</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Issuer Metadata</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Credential レスポンスの暗号化に対応する場合の設定。</t>
         </is>
       </c>
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>{ "alg_values_supported": ["ECDH-ES"], "enc_values_supported": ["A128GCM"], "encryption_required": true }</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>batch_credential_issuance</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2389,39 +2770,59 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>バッチ発行対応の宣言(HAIP では有無で対応可否を明示する MUST)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+          <t>バッチ発行対応の宣言(HAIPでは有無で対応可否を明示する MUST)。</t>
+        </is>
+      </c>
+      <c r="E14" s="15" t="inlineStr">
+        <is>
+          <t>{ "batch_size": 10 }</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="57" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>signed_metadata</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Issuer Metadata</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>署名付きメタデータを使う場合に含める(HAIP では条件付き MUST)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>署名付きメタデータを使う場合に含める(HAIPでは条件付き MUST)。</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>"eyJhbGciOiJFUzI1NiIsIng1YyI6WyJNSUlDLi4uIl19.eyJjcmVkZW50aWFsX2lzc3Vlci..."</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="72" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>display</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2434,6 +2835,16 @@
       <c r="D16" s="14" t="inlineStr">
         <is>
           <t>発行者名やロゴ等の国際化表示情報。</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>[{ "name": "Example Bank", "locale": "en-US", "logo": { "uri": "https://.../logo.png" } }]</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
@@ -2446,158 +2857,230 @@
       <c r="B17" s="10" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>各 Credential 構成</t>
+          <t>各Credential構成</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>クレデンシャル形式識別子(dc+sd-jwt, mso_mdoc 等)。</t>
+          <t>クレデンシャル形式識別子。</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>"dc+sd-jwt"   /   "mso_mdoc"</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="19" ht="42" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t>scope</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>各 Credential 構成</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>認可リクエスト用の scope 値(HAIP では全構成に付与する MUST)。</t>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>各Credential構成</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>認可リクエスト用の scope 値(HAIPでは全構成に付与する MUST)。</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>"employee_credential"</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>cryptographic_binding_methods_supported</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>各 Credential 構成</t>
+          <t>各Credential構成</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>鍵バインディング方式(jwk 等)。存在すると nonce_endpoint が必須化。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
+          <t>鍵バインディング方式。存在すると nonce_endpoint が必須化。</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>["jwk"]</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t>credential_signing_alg_values_supported</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>各 Credential 構成</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>各Credential構成</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>クレデンシャル署名アルゴリズム候補。</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>["ES256"]</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="57" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>proof_types_supported</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>各 Credential 構成</t>
+          <t>各Credential構成</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>鍵バインディングを行う場合に必須。proof の型(jwt, attestation)を規定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+          <t>鍵バインディングを行う場合に必須。proof の型を規定。</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>{ "jwt": { "proof_signing_alg_values_supported": ["ES256"] } }</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="57" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>display</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>各 Credential 構成</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>各Credential構成</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>その構成の表示名・ロゴ・色等。</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>[{ "name": "社員証", "locale": "ja-JP", "background_color": "#12107c" }]</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="72" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>claims</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>各 Credential 構成</t>
+          <t>各Credential構成</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
           <t>クレデンシャル内クレームの定義・表示情報。</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>[{ "path": ["family_name"], "display": [{ "name": "姓", "locale": "ja-JP" }] }]</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Issuer Metadata</t>
         </is>
       </c>
     </row>
@@ -2610,14 +3093,16 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>credential_issuer</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2632,36 +3117,56 @@
           <t>オファー対象の発行者 URL。</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>"https://issuer.example.com"</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>credential_configuration_ids</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Credential Offer</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>オファーするクレデンシャル構成の ID 群。</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>["EmployeeCredential"]</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="72" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t>grants</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2676,36 +3181,56 @@
           <t>利用可能なグラント種別と付随情報。</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>{ "urn:ietf:params:oauth:grant-type:pre-authorized_code": { "pre-authorized_code": "Splx..." } }</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>grants.authorization_code.issuer_state</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Offer/grants</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>認可コードフローで発行者が状態を紐づける値。</t>
         </is>
       </c>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>"eyJhbGciOiJra...state"</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>grants.pre-authorized_code.pre-authorized_code</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2720,36 +3245,56 @@
           <t>事前認可コード(pre-authorized グラント使用時)。</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>"SplxlOBeZQQYbYS6WxSbIA"</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="57" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>grants.pre-authorized_code.tx_code</t>
         </is>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Offer/grants</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>別送する PIN(tx_code)の要求仕様。</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>{ "input_mode": "numeric", "length": 4, "description": "SMSのコードを入力" }</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>grants.*.authorization_server</t>
         </is>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -2761,7 +3306,17 @@
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>対象の認可サーバー(複数 AS 時)。</t>
+          <t>対象の認可サーバー(複数AS時)。</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>"https://as.example.com"</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Offer</t>
         </is>
       </c>
     </row>
@@ -2774,14 +3329,16 @@
       <c r="B33" s="10" t="n"/>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="10" t="n"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="87" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>authorization_details</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2796,26 +3353,46 @@
           <t>authorization_details を用いた場合に返却。</t>
         </is>
       </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>[{ "type": "openid_credential", "credential_configuration_id": "EmployeeCredential", "credential_identifiers": ["cred-1"] }]</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Token Response</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t>authorization_details[].credential_identifiers</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Token Response</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>authorization_details 内で発行対象を識別する ID。</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>["cred-1", "cred-2"]</t>
+        </is>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Token Response</t>
         </is>
       </c>
     </row>
@@ -2828,14 +3405,16 @@
       <c r="B36" s="10" t="n"/>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
     </row>
     <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>credential_identifier</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2850,36 +3429,56 @@
           <t>authorization_details 返却時に、それを参照して指定。</t>
         </is>
       </c>
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>"cred-1"</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Request</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t>credential_configuration_id</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Credential Request</t>
         </is>
       </c>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>credential_identifier を使わない場合に構成 ID を指定。</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>"EmployeeCredential"</t>
+        </is>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="57" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>proofs</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2894,26 +3493,46 @@
           <t>proof_types_supported がある場合に必須(複数形)。</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>{ "jwt": ["eyJ0eXAiOiJvcGVuaWQ0dmNpLXByb29mK2p3dCIsImFsZyI6IkVTMjU2Ii..."] }</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Request</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="72" customHeight="1">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>credential_response_encryption</t>
         </is>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Credential Request</t>
         </is>
       </c>
-      <c r="D40" s="18" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>レスポンス暗号化を要求する場合の鍵情報。</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>{ "jwk": { "kty":"EC","crv":"P-256","x":"...","y":"..." }, "alg": "ECDH-ES", "enc": "A128GCM" }</t>
+        </is>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Request</t>
         </is>
       </c>
     </row>
@@ -2926,14 +3545,16 @@
       <c r="B41" s="10" t="n"/>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="10" t="n"/>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+    </row>
+    <row r="42" ht="72" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
@@ -2948,36 +3569,56 @@
           <t>即時発行時に発行された VC 群(複数形)を返却。</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
+        <is>
+          <t>[{ "credential": "eyJ0eXAiOiJkYytzZC1qd3QiLCJhbGciOiJFUzI1NiJ9...~WyJfMjZi...~" }]</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B43" s="25" t="inlineStr">
         <is>
           <t>条件付き必須</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Credential Response</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="20" t="inlineStr">
         <is>
           <t>遅延発行時に、後で取得するための ID を返却。</t>
         </is>
       </c>
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>"8xLOxBtZp8"</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Response</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>interval</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="23" t="inlineStr">
         <is>
           <t>必須</t>
         </is>
@@ -2992,42 +3633,99 @@
           <t>transaction_id 使用時、再取得までの待機秒数。</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Response</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t>notification_id</t>
         </is>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="24" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Credential Response</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="20" t="inlineStr">
         <is>
           <t>通知エンドポイントと紐づける ID。</t>
         </is>
       </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>"3fwe98js"</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>OID4VCI §Credential Response</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D45"/>
+  <autoFilter ref="A4:F45"/>
   <mergeCells count="9">
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>